--- a/Employee_Reports_wi48/Sandy De Vera Apigo Q0090.xlsx
+++ b/Employee_Reports_wi48/Sandy De Vera Apigo Q0090.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-215</v>
+        <v>-218</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -619,11 +619,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-401</v>
+        <v>-404</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-350</v>
+        <v>-353</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -693,11 +693,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
